--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.33998023792034</v>
+        <v>8.505246788662056</v>
       </c>
       <c r="D2" t="n">
-        <v>50.52607354419448</v>
+        <v>8.210486950931603</v>
       </c>
       <c r="E2" t="n">
-        <v>10.60635349886492</v>
+        <v>1.723532443565549</v>
       </c>
       <c r="F2" t="n">
-        <v>10.40884217712797</v>
+        <v>1.691436853783295</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.75979576005883</v>
+        <v>9.22346681100956</v>
       </c>
       <c r="D3" t="n">
-        <v>55.24791340854048</v>
+        <v>8.977785928887828</v>
       </c>
       <c r="E3" t="n">
-        <v>10.60635349886492</v>
+        <v>1.723532443565549</v>
       </c>
       <c r="F3" t="n">
-        <v>10.40884217712797</v>
+        <v>1.691436853783295</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.70298411564613</v>
+        <v>6.939234918792496</v>
       </c>
       <c r="D4" t="n">
-        <v>41.13977982034348</v>
+        <v>6.685214220805817</v>
       </c>
       <c r="E4" t="n">
-        <v>10.60635349886492</v>
+        <v>1.723532443565549</v>
       </c>
       <c r="F4" t="n">
-        <v>10.40884217712797</v>
+        <v>1.691436853783295</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.153390934807</v>
+        <v>5.549926026906138</v>
       </c>
       <c r="D5" t="n">
-        <v>33.58939469063134</v>
+        <v>5.458276637227594</v>
       </c>
       <c r="E5" t="n">
-        <v>10.60635349886492</v>
+        <v>1.723532443565549</v>
       </c>
       <c r="F5" t="n">
-        <v>10.40884217712797</v>
+        <v>1.691436853783295</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.11282384042039</v>
+        <v>6.355833874068313</v>
       </c>
       <c r="D6" t="n">
-        <v>40.00229849013414</v>
+        <v>6.500373504646799</v>
       </c>
       <c r="E6" t="n">
-        <v>10.60635349886492</v>
+        <v>1.723532443565549</v>
       </c>
       <c r="F6" t="n">
-        <v>10.40884217712797</v>
+        <v>1.691436853783295</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.73632749210844</v>
+        <v>7.757153217467621</v>
       </c>
       <c r="D7" t="n">
-        <v>49.00522242225323</v>
+        <v>7.96334864361615</v>
       </c>
       <c r="E7" t="n">
-        <v>10.60635349886492</v>
+        <v>1.723532443565549</v>
       </c>
       <c r="F7" t="n">
-        <v>10.40884217712797</v>
+        <v>1.691436853783295</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.21785922754696</v>
+        <v>3.610402124476382</v>
       </c>
       <c r="D8" t="n">
-        <v>23.94787561644797</v>
+        <v>3.891529787672795</v>
       </c>
       <c r="E8" t="n">
-        <v>10.60635349886492</v>
+        <v>1.723532443565549</v>
       </c>
       <c r="F8" t="n">
-        <v>10.40884217712797</v>
+        <v>1.691436853783295</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.5761291715126</v>
+        <v>5.456120990370798</v>
       </c>
       <c r="D9" t="n">
-        <v>35.22823972416163</v>
+        <v>5.724588955176266</v>
       </c>
       <c r="E9" t="n">
-        <v>10.60635349886492</v>
+        <v>1.723532443565549</v>
       </c>
       <c r="F9" t="n">
-        <v>10.40884217712797</v>
+        <v>1.691436853783295</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>56.66834500484467</v>
+        <v>9.20860606328726</v>
       </c>
       <c r="D10" t="n">
-        <v>58.35895624966339</v>
+        <v>9.483330390570302</v>
       </c>
       <c r="E10" t="n">
-        <v>10.60635349886492</v>
+        <v>1.723532443565549</v>
       </c>
       <c r="F10" t="n">
-        <v>10.40884217712797</v>
+        <v>1.691436853783295</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>49.50103134950162</v>
+        <v>8.043917594294014</v>
       </c>
       <c r="D11" t="n">
-        <v>51.31044184094196</v>
+        <v>8.337946799153068</v>
       </c>
       <c r="E11" t="n">
-        <v>10.60635349886492</v>
+        <v>1.723532443565549</v>
       </c>
       <c r="F11" t="n">
-        <v>10.40884217712797</v>
+        <v>1.691436853783295</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>53.83097735865808</v>
+        <v>8.747533820781939</v>
       </c>
       <c r="D12" t="n">
-        <v>55.64112122906376</v>
+        <v>9.04168219972286</v>
       </c>
       <c r="E12" t="n">
-        <v>10.60635349886492</v>
+        <v>1.723532443565549</v>
       </c>
       <c r="F12" t="n">
-        <v>10.40884217712797</v>
+        <v>1.691436853783295</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
